--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06-21T16:40:10</t>
+          <t>2026-06-25T21:05:37</t>
         </is>
       </c>
     </row>

--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06-25T21:05:37</t>
+          <t>2026-06-25T22:03:42</t>
         </is>
       </c>
     </row>
